--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationadministration.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -705,7 +705,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -799,7 +799,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1012,7 +1012,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1036,7 +1036,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1134,7 +1134,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1287,7 +1287,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1356,7 +1356,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1463,7 +1463,7 @@
     <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1487,7 +1487,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1785,7 +1785,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1830,7 +1830,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
